--- a/Check.xlsx
+++ b/Check.xlsx
@@ -691,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -717,6 +717,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Java UI-автоматизация</t>
+        </is>
+      </c>
     </row>
     <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
@@ -732,6 +737,11 @@
         <v>7</v>
       </c>
       <c r="E2" s="2"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: LoginPage.checkLoginScreen (проверяется в предусловии AuthTest/NavigationTest)</t>
+        </is>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
@@ -749,6 +759,11 @@
       <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: AuthTest.successfulLogin</t>
+        </is>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -766,6 +781,11 @@
       <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: AuthTest.loginWithUnregisteredUser</t>
+        </is>
+      </c>
     </row>
     <row r="5" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -783,6 +803,11 @@
       <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: AuthTest.loginWithEmptyLogin</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -800,6 +825,11 @@
       <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: AuthTest.loginWithEmptyPassword</t>
+        </is>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -817,6 +847,11 @@
       <c r="E7" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: AuthTest.loginWithEmptyFields</t>
+        </is>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -832,6 +867,11 @@
         <v>15</v>
       </c>
       <c r="E8" s="2"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Не автоматизировано; ручной результат сохранён в столбце E.</t>
+        </is>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -849,6 +889,11 @@
       <c r="E9" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: Проверяется отказ во входе; нестабильный текст ошибки не сверяется</t>
+        </is>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -864,6 +909,11 @@
         <v>7</v>
       </c>
       <c r="E10" s="2"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Не автоматизировано; ручной результат сохранён в столбце E.</t>
+        </is>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -879,6 +929,11 @@
         <v>7</v>
       </c>
       <c r="E11" s="2"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: AuthTest.loginWithEmptyFields</t>
+        </is>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -894,6 +949,11 @@
         <v>7</v>
       </c>
       <c r="E12" s="2"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: MainPage.checkMainScreen</t>
+        </is>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -909,6 +969,11 @@
         <v>7</v>
       </c>
       <c r="E13" s="2"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: MainPage.checkMainScreen</t>
+        </is>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -924,6 +989,11 @@
         <v>7</v>
       </c>
       <c r="E14" s="2"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NavigationTest.openNewsFromMenu</t>
+        </is>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -939,6 +1009,11 @@
         <v>7</v>
       </c>
       <c r="E15" s="2"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NavigationTest.openNewsFromMenu</t>
+        </is>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -954,6 +1029,11 @@
         <v>7</v>
       </c>
       <c r="E16" s="2"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NavigationTest.openNewsFromMenu</t>
+        </is>
+      </c>
     </row>
     <row r="17" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -969,6 +1049,11 @@
         <v>15</v>
       </c>
       <c r="E17" s="2"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NavigationTest.openNewsFromMenu</t>
+        </is>
+      </c>
     </row>
     <row r="18" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -986,6 +1071,11 @@
       <c r="E18" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NavigationTest.openNewsFromMenu</t>
+        </is>
+      </c>
     </row>
     <row r="19" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
@@ -1001,6 +1091,11 @@
         <v>7</v>
       </c>
       <c r="E19" s="2"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NavigationTest.openAllNews</t>
+        </is>
+      </c>
     </row>
     <row r="20" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
@@ -1018,6 +1113,11 @@
       <c r="E20" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NavigationTest.openAllNews</t>
+        </is>
+      </c>
     </row>
     <row r="21" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -1033,6 +1133,11 @@
         <v>15</v>
       </c>
       <c r="E21" s="2"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NavigationTest.openThematicQuotes</t>
+        </is>
+      </c>
     </row>
     <row r="22" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -1048,6 +1153,11 @@
         <v>15</v>
       </c>
       <c r="E22" s="2"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Не автоматизировано; ручной результат сохранён в столбце E.</t>
+        </is>
+      </c>
     </row>
     <row r="23" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
@@ -1063,6 +1173,11 @@
         <v>7</v>
       </c>
       <c r="E23" s="2"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NavigationTest.openNewsFromMenu</t>
+        </is>
+      </c>
     </row>
     <row r="24" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
@@ -1078,6 +1193,11 @@
         <v>7</v>
       </c>
       <c r="E24" s="2"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsListPage.checkNewsScreenDisplayed</t>
+        </is>
+      </c>
     </row>
     <row r="25" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
@@ -1093,6 +1213,11 @@
         <v>7</v>
       </c>
       <c r="E25" s="2"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.viewNewsInControlPanel</t>
+        </is>
+      </c>
     </row>
     <row r="26" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
@@ -1108,6 +1233,11 @@
         <v>7</v>
       </c>
       <c r="E26" s="2"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.viewNewsInControlPanel</t>
+        </is>
+      </c>
     </row>
     <row r="27" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -1123,6 +1253,11 @@
         <v>7</v>
       </c>
       <c r="E27" s="2"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Не автоматизировано; ручной результат сохранён в столбце E.</t>
+        </is>
+      </c>
     </row>
     <row r="28" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
@@ -1138,6 +1273,11 @@
         <v>7</v>
       </c>
       <c r="E28" s="2"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.viewNewsInControlPanel</t>
+        </is>
+      </c>
     </row>
     <row r="29" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
@@ -1153,6 +1293,11 @@
         <v>15</v>
       </c>
       <c r="E29" s="2"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Не автоматизировано; ручной результат сохранён в столбце E.</t>
+        </is>
+      </c>
     </row>
     <row r="30" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
@@ -1168,6 +1313,11 @@
         <v>7</v>
       </c>
       <c r="E30" s="2"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.viewNewsInControlPanel</t>
+        </is>
+      </c>
     </row>
     <row r="31" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
@@ -1185,6 +1335,11 @@
       <c r="E31" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsFilterTest.sortNewsByPublishDate</t>
+        </is>
+      </c>
     </row>
     <row r="32" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
@@ -1200,6 +1355,11 @@
         <v>7</v>
       </c>
       <c r="E32" s="2"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: FilterNewsPage.checkFilterScreen; NewsFilterTest.</t>
+        </is>
+      </c>
     </row>
     <row r="33" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
@@ -1217,6 +1377,11 @@
       <c r="E33" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsFilterTest.filterByAnnouncement</t>
+        </is>
+      </c>
     </row>
     <row r="34" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
@@ -1234,6 +1399,11 @@
       <c r="E34" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsFilterTest.filterByBirthday</t>
+        </is>
+      </c>
     </row>
     <row r="35" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -1251,6 +1421,11 @@
       <c r="E35" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsFilterTest.filterBySalary</t>
+        </is>
+      </c>
     </row>
     <row r="36" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
@@ -1268,6 +1443,11 @@
       <c r="E36" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsFilterTest.filterByUnion</t>
+        </is>
+      </c>
     </row>
     <row r="37" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
@@ -1285,6 +1465,11 @@
       <c r="E37" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsFilterTest.filterByHoliday</t>
+        </is>
+      </c>
     </row>
     <row r="38" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
@@ -1300,6 +1485,11 @@
         <v>48</v>
       </c>
       <c r="E38" s="2"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsFilterTest.filterByMassage</t>
+        </is>
+      </c>
     </row>
     <row r="39" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
@@ -1315,6 +1505,11 @@
         <v>48</v>
       </c>
       <c r="E39" s="2"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsFilterTest.filterByGratitude</t>
+        </is>
+      </c>
     </row>
     <row r="40" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
@@ -1332,6 +1527,11 @@
       <c r="E40" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsFilterTest.filterByHelp</t>
+        </is>
+      </c>
     </row>
     <row r="41" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
@@ -1349,6 +1549,11 @@
       <c r="E41" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsFilterTest.applyFilterWithoutCategory</t>
+        </is>
+      </c>
     </row>
     <row r="42" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
@@ -1366,6 +1571,11 @@
       <c r="E42" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Не автоматизировано; ручной результат сохранён в столбце E.</t>
+        </is>
+      </c>
     </row>
     <row r="43" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
@@ -1381,6 +1591,11 @@
         <v>15</v>
       </c>
       <c r="E43" s="2"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Не автоматизировано; ручной результат сохранён в столбце E.</t>
+        </is>
+      </c>
     </row>
     <row r="44" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
@@ -1396,6 +1611,11 @@
         <v>15</v>
       </c>
       <c r="E44" s="2"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Не автоматизировано; ручной результат сохранён в столбце E.</t>
+        </is>
+      </c>
     </row>
     <row r="45" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
@@ -1411,6 +1631,11 @@
         <v>7</v>
       </c>
       <c r="E45" s="2"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsFilterTest.resetFilter</t>
+        </is>
+      </c>
     </row>
     <row r="46" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
@@ -1426,6 +1651,11 @@
         <v>7</v>
       </c>
       <c r="E46" s="2"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsFilterTest.resetFilter</t>
+        </is>
+      </c>
     </row>
     <row r="47" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
@@ -1441,6 +1671,11 @@
         <v>7</v>
       </c>
       <c r="E47" s="2"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest / NewsFilterTest: открытие панели управления</t>
+        </is>
+      </c>
     </row>
     <row r="48" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
@@ -1456,6 +1691,11 @@
         <v>7</v>
       </c>
       <c r="E48" s="2"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest / NewsFilterTest</t>
+        </is>
+      </c>
     </row>
     <row r="49" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
@@ -1471,6 +1711,11 @@
         <v>15</v>
       </c>
       <c r="E49" s="2"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.sortNewsInControlPanel</t>
+        </is>
+      </c>
     </row>
     <row r="50" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
@@ -1486,6 +1731,11 @@
         <v>7</v>
       </c>
       <c r="E50" s="2"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.viewNewsInControlPanel</t>
+        </is>
+      </c>
     </row>
     <row r="51" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
@@ -1501,6 +1751,11 @@
         <v>7</v>
       </c>
       <c r="E51" s="2"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.createNews</t>
+        </is>
+      </c>
     </row>
     <row r="52" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
@@ -1518,6 +1773,11 @@
       <c r="E52" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.createNews</t>
+        </is>
+      </c>
     </row>
     <row r="53" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
@@ -1535,6 +1795,11 @@
       <c r="E53" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.createNewsWithoutCategory</t>
+        </is>
+      </c>
     </row>
     <row r="54" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
@@ -1552,6 +1817,11 @@
       <c r="E54" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.createNewsWithoutDate</t>
+        </is>
+      </c>
     </row>
     <row r="55" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
@@ -1569,6 +1839,11 @@
       <c r="E55" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.createNewsWithoutTime</t>
+        </is>
+      </c>
     </row>
     <row r="56" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
@@ -1586,6 +1861,11 @@
       <c r="E56" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.createNewsWithoutDescription</t>
+        </is>
+      </c>
     </row>
     <row r="57" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
@@ -1603,6 +1883,11 @@
       <c r="E57" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.createNewsWithoutTitle</t>
+        </is>
+      </c>
     </row>
     <row r="58" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
@@ -1618,6 +1903,11 @@
         <v>7</v>
       </c>
       <c r="E58" s="2"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: Проверяется, что форма остаётся открытой; текст Toast не сверяется</t>
+        </is>
+      </c>
     </row>
     <row r="59" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
@@ -1635,6 +1925,11 @@
       <c r="E59" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.editNews</t>
+        </is>
+      </c>
     </row>
     <row r="60" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
@@ -1650,6 +1945,11 @@
         <v>7</v>
       </c>
       <c r="E60" s="2"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Не автоматизировано; ручной результат сохранён в столбце E.</t>
+        </is>
+      </c>
     </row>
     <row r="61" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
@@ -1665,6 +1965,11 @@
         <v>15</v>
       </c>
       <c r="E61" s="2"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Не автоматизировано; ручной результат сохранён в столбце E.</t>
+        </is>
+      </c>
     </row>
     <row r="62" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
@@ -1682,6 +1987,11 @@
       <c r="E62" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.deleteNews</t>
+        </is>
+      </c>
     </row>
     <row r="63" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
@@ -1697,6 +2007,11 @@
         <v>15</v>
       </c>
       <c r="E63" s="2"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Не автоматизировано; ручной результат сохранён в столбце E.</t>
+        </is>
+      </c>
     </row>
     <row r="64" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
@@ -1714,6 +2029,11 @@
       <c r="E64" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.changeNewsStatusToInactive</t>
+        </is>
+      </c>
     </row>
     <row r="65" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
@@ -1729,6 +2049,11 @@
         <v>15</v>
       </c>
       <c r="E65" s="2"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.filterActiveNews</t>
+        </is>
+      </c>
     </row>
     <row r="66" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
@@ -1744,6 +2069,11 @@
         <v>15</v>
       </c>
       <c r="E66" s="2"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NewsTest.filterInactiveNews</t>
+        </is>
+      </c>
     </row>
     <row r="67" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
@@ -1761,6 +2091,11 @@
       <c r="E67" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NavigationTest.openThematicQuotes</t>
+        </is>
+      </c>
     </row>
     <row r="68" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
@@ -1776,6 +2111,11 @@
         <v>15</v>
       </c>
       <c r="E68" s="2"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: NavigationTest.openThematicQuotes</t>
+        </is>
+      </c>
     </row>
     <row r="69" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
@@ -1791,6 +2131,11 @@
         <v>15</v>
       </c>
       <c r="E69" s="2"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: QuotesTest.expandAndCollapseQuote</t>
+        </is>
+      </c>
     </row>
     <row r="70" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
@@ -1806,6 +2151,11 @@
         <v>15</v>
       </c>
       <c r="E70" s="2"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: QuotesTest.expandAndCollapseQuote</t>
+        </is>
+      </c>
     </row>
     <row r="71" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
@@ -1823,6 +2173,11 @@
       <c r="E71" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: QuotesTest.expandAndCollapseQuote</t>
+        </is>
+      </c>
     </row>
     <row r="72" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
@@ -1840,6 +2195,11 @@
       <c r="E72" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: QuotesTest.expandAndCollapseQuote</t>
+        </is>
+      </c>
     </row>
     <row r="73" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
@@ -1855,6 +2215,11 @@
         <v>15</v>
       </c>
       <c r="E73" s="2"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Не автоматизировано; ручной результат сохранён в столбце E.</t>
+        </is>
+      </c>
     </row>
     <row r="74" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
@@ -1870,6 +2235,11 @@
         <v>15</v>
       </c>
       <c r="E74" s="2"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Не автоматизировано; ручной результат сохранён в столбце E.</t>
+        </is>
+      </c>
     </row>
     <row r="75" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
@@ -1885,6 +2255,11 @@
         <v>15</v>
       </c>
       <c r="E75" s="2"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Не автоматизировано; ручной результат сохранён в столбце E.</t>
+        </is>
+      </c>
     </row>
     <row r="76" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
@@ -1900,6 +2275,11 @@
         <v>7</v>
       </c>
       <c r="E76" s="2"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Автотест пройден: Переходы проверяются в NavigationTest; отдельного стресс-сценария нет</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E76" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1960,16 +2340,20 @@
       <c r="A6" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>94</v>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Проверки экрана «Наша Миссия» включены в сценарии тематических цитат.</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>96</v>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Уточнены сценарии тематических цитат, Main, ALL NEWS и перехода через меню.</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
